--- a/staging/breach datastructures.xlsx
+++ b/staging/breach datastructures.xlsx
@@ -8,13 +8,15 @@
     <sheet state="visible" name="FNC" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="HAK" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="SYS" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="PSV" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="DEK" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="HST" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="UPG" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="dataset notes" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="param notes" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="gameplay conventions" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="BOS" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="PSV" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="DEK" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="HST" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="UPG" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="dataset notes" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="param notes" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="gameplay conventions" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="boss passive notes" sheetId="14" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -22,17 +24,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="331">
   <si>
     <t>PRG_ID</t>
   </si>
   <si>
+    <t>FNC_ID</t>
+  </si>
+  <si>
     <t>HAK_ID</t>
   </si>
   <si>
-    <t>FNC_ID</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -42,264 +44,264 @@
     <t>cost</t>
   </si>
   <si>
+    <t>BASE_LINK</t>
+  </si>
+  <si>
     <t>shapes</t>
   </si>
   <si>
-    <t>BASE_LINK</t>
-  </si>
-  <si>
     <t>payload</t>
   </si>
   <si>
+    <t>STRONG_COLORS</t>
+  </si>
+  <si>
     <t>functions</t>
   </si>
   <si>
-    <t>STRONG_COLORS</t>
+    <t>STRONG_SHAPES</t>
+  </si>
+  <si>
+    <t>PRG_SET</t>
   </si>
   <si>
     <t>notes</t>
   </si>
   <si>
-    <t>STRONG_SHAPES</t>
+    <t>PASSIVES</t>
+  </si>
+  <si>
+    <t>PRG_H_001</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>BOMBER</t>
+  </si>
+  <si>
+    <t>PRG_S_001</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>GRAPHICS</t>
   </si>
   <si>
     <t>quantity</t>
   </si>
   <si>
-    <t>PRG_SET</t>
-  </si>
-  <si>
-    <t>PRG_S_001</t>
+    <t>E-BOMBER</t>
+  </si>
+  <si>
+    <t>TRI</t>
+  </si>
+  <si>
+    <t>HAK_01</t>
+  </si>
+  <si>
+    <t>FNC_001</t>
+  </si>
+  <si>
+    <t>CR45H</t>
+  </si>
+  <si>
+    <t>PRG_H_002</t>
+  </si>
+  <si>
+    <t>FNC_005</t>
+  </si>
+  <si>
+    <t>BUFFER</t>
+  </si>
+  <si>
+    <t>RED:GRE:YEL</t>
+  </si>
+  <si>
+    <t>TRI:SQU:STR</t>
+  </si>
+  <si>
+    <t>PRG_S_002</t>
+  </si>
+  <si>
+    <t>GRE</t>
+  </si>
+  <si>
+    <t>PRG_H_001:PRG_H_002:PRG_H_005</t>
+  </si>
+  <si>
+    <t>SHIELDER</t>
+  </si>
+  <si>
+    <t>PSV_001:PSV_002</t>
+  </si>
+  <si>
+    <t>SQU</t>
+  </si>
+  <si>
+    <t>hacker biography goes here</t>
+  </si>
+  <si>
+    <t>hacker graphics reference goes here</t>
+  </si>
+  <si>
+    <t>FNC_002</t>
   </si>
   <si>
     <t>countdown</t>
   </si>
   <si>
-    <t>E-BOMBER</t>
-  </si>
-  <si>
-    <t>PASSIVES</t>
+    <t>PRG_H_003</t>
+  </si>
+  <si>
+    <t>FNC_006</t>
   </si>
   <si>
     <t>areaPattern</t>
   </si>
   <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>BIO</t>
-  </si>
-  <si>
-    <t>TRI</t>
-  </si>
-  <si>
-    <t>GRAPHICS</t>
+    <t>ATTACKER</t>
+  </si>
+  <si>
+    <t>YEL</t>
+  </si>
+  <si>
+    <t>PRG_S_003</t>
   </si>
   <si>
     <t>magnitude</t>
   </si>
   <si>
-    <t>FNC_005</t>
-  </si>
-  <si>
-    <t>HAK_01</t>
+    <t>STR</t>
+  </si>
+  <si>
+    <t>FNC_003</t>
   </si>
   <si>
     <t>damage</t>
   </si>
   <si>
-    <t>CR45H</t>
+    <t>PRG_H_004</t>
   </si>
   <si>
     <t>startCharged</t>
   </si>
   <si>
-    <t>PRG_S_002</t>
-  </si>
-  <si>
-    <t>PRG_H_001</t>
-  </si>
-  <si>
-    <t>SHIELDER</t>
+    <t>DISABLER</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>CIR</t>
+  </si>
+  <si>
+    <t>PRG_S_004</t>
   </si>
   <si>
     <t>axisTarget</t>
   </si>
   <si>
-    <t>BOMBER</t>
-  </si>
-  <si>
-    <t>GRE</t>
-  </si>
-  <si>
-    <t>RED:GRE:YEL</t>
+    <t>FNC_004</t>
   </si>
   <si>
     <t>axisResult</t>
   </si>
   <si>
-    <t>SQU</t>
-  </si>
-  <si>
-    <t>TRI:SQU:STR</t>
-  </si>
-  <si>
-    <t>FNC_006</t>
+    <t>PRG_H_005</t>
+  </si>
+  <si>
+    <t>NINJA</t>
   </si>
   <si>
     <t>params</t>
   </si>
   <si>
-    <t>PRG_H_001:PRG_H_002:PRG_H_005</t>
-  </si>
-  <si>
-    <t>FNC_001</t>
-  </si>
-  <si>
-    <t>PSV_001:PSV_002</t>
-  </si>
-  <si>
-    <t>PRG_S_003</t>
-  </si>
-  <si>
-    <t>hacker biography goes here</t>
-  </si>
-  <si>
-    <t>ATTACKER</t>
-  </si>
-  <si>
-    <t>hacker graphics reference goes here</t>
-  </si>
-  <si>
-    <t>PRG_H_002</t>
+    <t>MAG</t>
+  </si>
+  <si>
+    <t>CRO</t>
+  </si>
+  <si>
+    <t>FNC_011</t>
   </si>
   <si>
     <t>BOMB</t>
   </si>
   <si>
-    <t>YEL</t>
-  </si>
-  <si>
-    <t>BUFFER</t>
-  </si>
-  <si>
-    <t>STR</t>
-  </si>
-  <si>
-    <t>FNC_003</t>
+    <t>PRG_H_006</t>
+  </si>
+  <si>
+    <t>PRG_S_005</t>
+  </si>
+  <si>
+    <t>WEASEL</t>
+  </si>
+  <si>
+    <t>MUSCLE</t>
   </si>
   <si>
     <t>EFFECT_BOMB</t>
   </si>
   <si>
+    <t>FNC_012</t>
+  </si>
+  <si>
+    <t>FNC_013</t>
+  </si>
+  <si>
     <t>generic bomb effect</t>
   </si>
   <si>
-    <t>FNC_002</t>
-  </si>
-  <si>
-    <t>PRG_S_004</t>
-  </si>
-  <si>
-    <t>DISABLER</t>
+    <t>PRG_S_006</t>
   </si>
   <si>
     <t>AREA_SQUARE_3X3</t>
   </si>
   <si>
-    <t>BLU</t>
-  </si>
-  <si>
-    <t>PRG_H_003</t>
-  </si>
-  <si>
-    <t>CIR</t>
-  </si>
-  <si>
-    <t>FNC_004</t>
+    <t>ENHANCE</t>
   </si>
   <si>
     <t>0:0:1</t>
   </si>
   <si>
-    <t>PRG_S_005</t>
-  </si>
-  <si>
-    <t>MUSCLE</t>
-  </si>
-  <si>
-    <t>CRO</t>
-  </si>
-  <si>
-    <t>FNC_013</t>
-  </si>
-  <si>
-    <t>PRG_H_004</t>
-  </si>
-  <si>
-    <t>PRG_S_006</t>
+    <t>FNC_014</t>
+  </si>
+  <si>
+    <t>PRG_S_007</t>
+  </si>
+  <si>
+    <t>SPAMBOT</t>
+  </si>
+  <si>
+    <t>FNC_015</t>
+  </si>
+  <si>
+    <t>PRG_S_008</t>
+  </si>
+  <si>
+    <t>THROWER</t>
   </si>
   <si>
     <t>BUFF</t>
   </si>
   <si>
-    <t>ENHANCE</t>
-  </si>
-  <si>
-    <t>MAG</t>
-  </si>
-  <si>
     <t>EFFECT_BUFF</t>
   </si>
   <si>
     <t>player buffer</t>
   </si>
   <si>
-    <t>FNC_014</t>
-  </si>
-  <si>
-    <t>PRG_H_005</t>
-  </si>
-  <si>
-    <t>NINJA</t>
-  </si>
-  <si>
-    <t>PRG_S_007</t>
-  </si>
-  <si>
-    <t>SPAMBOT</t>
-  </si>
-  <si>
-    <t>FNC_011</t>
-  </si>
-  <si>
-    <t>FNC_015</t>
-  </si>
-  <si>
     <t>ATTACK</t>
   </si>
   <si>
-    <t>PRG_H_006</t>
-  </si>
-  <si>
-    <t>PRG_S_008</t>
-  </si>
-  <si>
-    <t>WEASEL</t>
-  </si>
-  <si>
-    <t>THROWER</t>
-  </si>
-  <si>
     <t>EFFECT_ATTACK</t>
   </si>
   <si>
     <t>direct damage to opponent</t>
   </si>
   <si>
-    <t>FNC_012</t>
-  </si>
-  <si>
     <t>DRAIN</t>
   </si>
   <si>
@@ -447,6 +449,33 @@
     <t>turn other packets into magenta</t>
   </si>
   <si>
+    <t>FNC_018</t>
+  </si>
+  <si>
+    <t>DATABEND</t>
+  </si>
+  <si>
+    <t>supports ODANSHAY's passive</t>
+  </si>
+  <si>
+    <t>1:2:1:2</t>
+  </si>
+  <si>
+    <t>FNC_019</t>
+  </si>
+  <si>
+    <t>REBOOT</t>
+  </si>
+  <si>
+    <t>1:1:0:0</t>
+  </si>
+  <si>
+    <t>FNC_020</t>
+  </si>
+  <si>
+    <t>CODESHATTER</t>
+  </si>
+  <si>
     <t>SYS_ID</t>
   </si>
   <si>
@@ -465,72 +494,96 @@
     <t>PRG_S_003:PRG_S_005:PRG_S_006:PRG_S_001</t>
   </si>
   <si>
+    <t>system biography goes here</t>
+  </si>
+  <si>
+    <t>system graphics reference goes here</t>
+  </si>
+  <si>
+    <t>SYS_02</t>
+  </si>
+  <si>
+    <t>MIDNIGHT</t>
+  </si>
+  <si>
+    <t>BOS_ID</t>
+  </si>
+  <si>
+    <t>RED:MAG:BLU</t>
+  </si>
+  <si>
+    <t>PRG_S_007:PRG_S_008:PRG_S_001:PRG_S_002</t>
+  </si>
+  <si>
+    <t>system bio goes here</t>
+  </si>
+  <si>
+    <t>system graphics go here</t>
+  </si>
+  <si>
+    <t>SYS_03</t>
+  </si>
+  <si>
+    <t>DOORMAN</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>GRE:YEL:BLU</t>
+  </si>
+  <si>
+    <t>CIR:CRO:STR</t>
+  </si>
+  <si>
+    <t>BOSS_PASSIVE_DESCRIPTION</t>
+  </si>
+  <si>
+    <t>PRG_S_001:PRG_S_002:PRG_S_003:PRG_S_004</t>
+  </si>
+  <si>
+    <t>BOS_01</t>
+  </si>
+  <si>
+    <t>ODANSHAY</t>
+  </si>
+  <si>
+    <t>GRE:BLU:MAG</t>
+  </si>
+  <si>
+    <t>SQU:CIR:DIA</t>
+  </si>
+  <si>
+    <t>PRG_S_004:PRG_S_002:PRG_S_007:PRG_S_003</t>
+  </si>
+  <si>
+    <t>boss passive description goes here</t>
+  </si>
+  <si>
     <t>PASSIVE_ID</t>
   </si>
   <si>
-    <t>system biography goes here</t>
-  </si>
-  <si>
-    <t>system graphics reference goes here</t>
-  </si>
-  <si>
-    <t>SYS_02</t>
-  </si>
-  <si>
     <t>passive_effect</t>
   </si>
   <si>
-    <t>MIDNIGHT</t>
-  </si>
-  <si>
-    <t>RED:MAG:BLU</t>
-  </si>
-  <si>
     <t>activation</t>
   </si>
   <si>
-    <t>PRG_S_007:PRG_S_008:PRG_S_001:PRG_S_002</t>
-  </si>
-  <si>
     <t>function_payload</t>
   </si>
   <si>
-    <t>system bio goes here</t>
-  </si>
-  <si>
-    <t>system graphics go here</t>
-  </si>
-  <si>
     <t>agent_scope</t>
   </si>
   <si>
     <t>display</t>
   </si>
   <si>
-    <t>SYS_03</t>
-  </si>
-  <si>
-    <t>DOORMAN</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>GRE:YEL:BLU</t>
-  </si>
-  <si>
     <t>PSV_001</t>
   </si>
   <si>
-    <t>CIR:CRO:STR</t>
-  </si>
-  <si>
     <t>PSV_EXTRA_MATCH_DAMAGE</t>
   </si>
   <si>
-    <t>PRG_S_001:PRG_S_002:PRG_S_003:PRG_S_004</t>
-  </si>
-  <si>
     <t>RED:1</t>
   </si>
   <si>
@@ -549,48 +602,87 @@
     <t>PSV_EXTRA_MATCH_CHARGE</t>
   </si>
   <si>
+    <t>Gain %1 extra charge on a %0 sync</t>
+  </si>
+  <si>
+    <t>PSV_003</t>
+  </si>
+  <si>
+    <t>PSV_CHARGE_DAMPEN</t>
+  </si>
+  <si>
+    <t>ALL:1</t>
+  </si>
+  <si>
+    <t>ENEMY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%0 syncs generate %1 fewer charge </t>
+  </si>
+  <si>
+    <t>PSV_004</t>
+  </si>
+  <si>
+    <t>PSV_FUNCTION_DAMAGE_INCREASE</t>
+  </si>
+  <si>
+    <t>ALL:2</t>
+  </si>
+  <si>
+    <t>Increase damage dealt by %0 FUNCTIONS by %1</t>
+  </si>
+  <si>
+    <t>PSV_005</t>
+  </si>
+  <si>
+    <t>PSV_PERM_SHIELD</t>
+  </si>
+  <si>
+    <t>Decrease damage dealt from %0 sources by %1</t>
+  </si>
+  <si>
+    <t>PSV_006</t>
+  </si>
+  <si>
+    <t>YEL:1</t>
+  </si>
+  <si>
+    <t>PSV_007</t>
+  </si>
+  <si>
+    <t>PSV_BIGGER_BOMB</t>
+  </si>
+  <si>
+    <t>Increased explosion radius for all bombs</t>
+  </si>
+  <si>
+    <t>PSV_008</t>
+  </si>
+  <si>
+    <t>PSV_CARRIER</t>
+  </si>
+  <si>
+    <t>START_OF_TURN</t>
+  </si>
+  <si>
+    <t>PSV_009</t>
+  </si>
+  <si>
     <t>DEK_ID</t>
   </si>
   <si>
-    <t>Gain %1 extra charge on a %0 sync</t>
-  </si>
-  <si>
     <t>ADD_LINK</t>
   </si>
   <si>
-    <t>PSV_003</t>
-  </si>
-  <si>
-    <t>PSV_CHARGE_DAMPEN</t>
-  </si>
-  <si>
-    <t>ALL:1</t>
-  </si>
-  <si>
     <t>FUNCTIONS</t>
   </si>
   <si>
-    <t>ENEMY</t>
-  </si>
-  <si>
     <t>DESCRIPT</t>
   </si>
   <si>
-    <t xml:space="preserve">%0 syncs generate %1 fewer charge </t>
-  </si>
-  <si>
-    <t>PSV_004</t>
-  </si>
-  <si>
-    <t>PSV_FUNCTION_DAMAGE_INCREASE</t>
-  </si>
-  <si>
     <t>DEK_01</t>
   </si>
   <si>
-    <t>ALL:2</t>
-  </si>
-  <si>
     <t>AGIMA</t>
   </si>
   <si>
@@ -603,45 +695,6 @@
     <t>graphics reference goes here</t>
   </si>
   <si>
-    <t>Increase damage dealt by %0 FUNCTIONS by %1</t>
-  </si>
-  <si>
-    <t>PSV_005</t>
-  </si>
-  <si>
-    <t>PSV_PERM_SHIELD</t>
-  </si>
-  <si>
-    <t>Decrease damage dealt from %0 sources by %1</t>
-  </si>
-  <si>
-    <t>PSV_006</t>
-  </si>
-  <si>
-    <t>YEL:1</t>
-  </si>
-  <si>
-    <t>PSV_007</t>
-  </si>
-  <si>
-    <t>PSV_BIGGER_BOMB</t>
-  </si>
-  <si>
-    <t>Increased explosion radius for all bombs</t>
-  </si>
-  <si>
-    <t>PSV_008</t>
-  </si>
-  <si>
-    <t>PSV_CARRIER</t>
-  </si>
-  <si>
-    <t>START_OF_TURN</t>
-  </si>
-  <si>
-    <t>PSV_009</t>
-  </si>
-  <si>
     <t>HOST_ID</t>
   </si>
   <si>
@@ -675,84 +728,120 @@
     <t>ARENA</t>
   </si>
   <si>
+    <t>HST_04</t>
+  </si>
+  <si>
+    <t>VERDUN</t>
+  </si>
+  <si>
+    <t>HST_05</t>
+  </si>
+  <si>
+    <t>WEEDS</t>
+  </si>
+  <si>
     <t>UPGRADE_ID</t>
   </si>
   <si>
-    <t>HST_04</t>
-  </si>
-  <si>
-    <t>VERDUN</t>
-  </si>
-  <si>
-    <t>HST_05</t>
-  </si>
-  <si>
-    <t>WEEDS</t>
-  </si>
-  <si>
     <t>effects are game actions will have a unique EFFECT_ID that is referenced in the function dataset</t>
   </si>
   <si>
+    <t>effects will be defined in the req doc including their required parameters and datatypes/validation/sanitycheck</t>
+  </si>
+  <si>
+    <t>area types:</t>
+  </si>
+  <si>
+    <t>area designators include all lower areas, centered on detonating gem</t>
+  </si>
+  <si>
     <t>UPG_01</t>
   </si>
   <si>
-    <t>effects will be defined in the req doc including their required parameters and datatypes/validation/sanitycheck</t>
-  </si>
-  <si>
     <t>BRACER</t>
   </si>
   <si>
+    <t>self only</t>
+  </si>
+  <si>
     <t>UPG_02</t>
   </si>
   <si>
     <t>GRACE</t>
   </si>
   <si>
+    <t>cardinal neighbors</t>
+  </si>
+  <si>
+    <t>square 3 tiles on each side</t>
+  </si>
+  <si>
     <t>UPG_03</t>
   </si>
   <si>
-    <t>area types:</t>
-  </si>
-  <si>
     <t>L33TSK1LL</t>
   </si>
   <si>
-    <t>area designators include all lower areas, centered on detonating gem</t>
+    <t>1 tile in each cardinal direction at a distance of 2 from the center</t>
   </si>
   <si>
     <t>UPG_04</t>
   </si>
   <si>
+    <t>runs consist of 4 battles 1 intro 2&amp;3 escalation 4 boss, currently only difficulty progression is increased ice for each won battle</t>
+  </si>
+  <si>
     <t>SNEAKERS</t>
   </si>
   <si>
-    <t>self only</t>
-  </si>
-  <si>
-    <t>cardinal neighbors</t>
-  </si>
-  <si>
-    <t>square 3 tiles on each side</t>
-  </si>
-  <si>
-    <t>1 tile in each cardinal direction at a distance of 2 from the center</t>
-  </si>
-  <si>
     <t>3 tiles in each cardinal direction at a distance of 2 from the center making a fat cross pattern</t>
   </si>
   <si>
+    <t>datastream composition</t>
+  </si>
+  <si>
+    <t>special packets</t>
+  </si>
+  <si>
+    <t>sync</t>
+  </si>
+  <si>
+    <t>during a run SYSTEM ICE starts at the system base ICE then this increases by 50 after the player wins a battle - for the current 4 battle system its +0, +50, +100, +150</t>
+  </si>
+  <si>
     <t>square of 5 tiles on each side</t>
   </si>
   <si>
+    <t>cascades</t>
+  </si>
+  <si>
+    <t>upgrades can't be duplicated, if there are less than 4 in the datasheet the game should error, each choice should be a unique upgrade but if there are fewer upgrades in the pool than the available number of route choices then the an upgrade can be listed in multiple choices</t>
+  </si>
+  <si>
+    <t>the game starts with an upgrade choice before the first battle but the system and host for both choices  always be DOORMAN and THRESHOLD</t>
+  </si>
+  <si>
     <t>3 tiles in each cardinal direction at a distance of 3 from the center making a fatter cross pattern</t>
   </si>
   <si>
     <t>square of 7 tiles on each side + 5 tiles in each cardinal direction making a very fat cross</t>
   </si>
   <si>
+    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
+  </si>
+  <si>
+    <t>0 - retain special packet overlays</t>
+  </si>
+  <si>
+    <t>0 - prevent sync after shake</t>
+  </si>
+  <si>
     <t>drain</t>
   </si>
   <si>
+    <t>0 - no cascades after sync</t>
+  </si>
+  <si>
     <t>name for disabler ability, potential for other disabling effects - currently targeted for hacker and deterministic as defined in the req for system, remove all charge from targeted unit</t>
   </si>
   <si>
@@ -765,6 +854,18 @@
     <t>description</t>
   </si>
   <si>
+    <t>1 - non-special packets randomized</t>
+  </si>
+  <si>
+    <t>1 - remove special packet overlays</t>
+  </si>
+  <si>
+    <t>1 - allow sync after shake</t>
+  </si>
+  <si>
+    <t>1 - cascades up to cascade limit</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
@@ -780,6 +881,12 @@
     <t>name displayed to player to identify item, non-unique names are not invalid but a warning is issued in the logs during init</t>
   </si>
   <si>
+    <t>2 - remove only enemy overlays</t>
+  </si>
+  <si>
+    <t>2 - unlmited cascades</t>
+  </si>
+  <si>
     <t>name of color match that charges unit, may have multiple entries separated by colon(:)</t>
   </si>
   <si>
@@ -792,46 +899,67 @@
     <t>id values of FNCs unit possesses, currently only a sigle FNC is allowed but planning for mulitple</t>
   </si>
   <si>
+    <t>dimension</t>
+  </si>
+  <si>
+    <t>targeting</t>
+  </si>
+  <si>
     <t>non-normative descriptions, explanations, and clarifications</t>
   </si>
   <si>
-    <t>datastream composition</t>
-  </si>
-  <si>
-    <t>special packets</t>
+    <t>special packets retention (retained packets with vertical space below them fall normally)</t>
+  </si>
+  <si>
+    <t>deal damage</t>
+  </si>
+  <si>
+    <t>gain charge</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>sync</t>
-  </si>
-  <si>
     <t>cost in charge to activate the FNC - a unit's charge pool is at minimum the size of its most costly FNC</t>
   </si>
   <si>
-    <t>cascades</t>
+    <t>0 - row</t>
+  </si>
+  <si>
+    <t>0 - random packet (not already sliced by current function acivation)</t>
+  </si>
+  <si>
+    <t>0 - destroy</t>
   </si>
   <si>
     <t>effect or other ability invoked when FNC is activated, may have multiple entires that are fired sequentially, to prevent looping it will be an error if an FNC has a an FNC payload that itself also has an FNC payload, self listing in payload is invalid</t>
   </si>
   <si>
+    <t>0 - sliced row deals damage according to activating user's c/s profile</t>
+  </si>
+  <si>
+    <t>0 - sliced packets in target row charge</t>
+  </si>
+  <si>
     <t>The number of discrete board-item deployments produced by one Effect resolution.</t>
   </si>
   <si>
+    <t>1 - column</t>
+  </si>
+  <si>
     <t>turns remaining before a placed countdown object resolves its associated Effect.</t>
   </si>
   <si>
-    <t>0 - existing board state (colors/shapes) retained and repositioned</t>
-  </si>
-  <si>
-    <t>0 - retain special packet overlays</t>
-  </si>
-  <si>
-    <t>0 - prevent sync after shake</t>
-  </si>
-  <si>
-    <t>0 - no cascades after sync</t>
+    <t>1 - targeted packet (not already sliced by current function activation)</t>
+  </si>
+  <si>
+    <t>1 - retain all</t>
+  </si>
+  <si>
+    <t>1 - no damage</t>
+  </si>
+  <si>
+    <t>1 - no charge</t>
   </si>
   <si>
     <t>the area of the board on which the effect occurs, using defined positions and not a mathematical calculation</t>
@@ -840,21 +968,12 @@
     <t>non-damage numeric value of the effect, interpreted per-effect feature</t>
   </si>
   <si>
+    <t>2 - retain only activating user specials</t>
+  </si>
+  <si>
     <t>damage done by the effect</t>
   </si>
   <si>
-    <t>1 - non-special packets randomized</t>
-  </si>
-  <si>
-    <t>1 - remove special packet overlays</t>
-  </si>
-  <si>
-    <t>1 - allow sync after shake</t>
-  </si>
-  <si>
-    <t>1 - cascades up to cascade limit</t>
-  </si>
-  <si>
     <t>colon (:) separated list of parameters specific to that function</t>
   </si>
   <si>
@@ -864,66 +983,15 @@
     <t>axisresult</t>
   </si>
   <si>
+    <t>targeteting</t>
+  </si>
+  <si>
     <t>axis value that the transform effect changes the targeted packet access into</t>
   </si>
   <si>
     <t>whether or not to include the item in the random pool for that item class, default is 'y'es</t>
   </si>
   <si>
-    <t>2 - unlmited cascades</t>
-  </si>
-  <si>
-    <t>dimension</t>
-  </si>
-  <si>
-    <t>targeting</t>
-  </si>
-  <si>
-    <t>special packets retention (retained packets with vertical space below them fall normally)</t>
-  </si>
-  <si>
-    <t>deal damage</t>
-  </si>
-  <si>
-    <t>gain charge</t>
-  </si>
-  <si>
-    <t>0 - row</t>
-  </si>
-  <si>
-    <t>0 - random packet (not already sliced by current function acivation)</t>
-  </si>
-  <si>
-    <t>0 - destroy</t>
-  </si>
-  <si>
-    <t>0 - sliced row deals damage according to activating user's c/s profile</t>
-  </si>
-  <si>
-    <t>0 - sliced packets in target row charge</t>
-  </si>
-  <si>
-    <t>1 - column</t>
-  </si>
-  <si>
-    <t>1 - targeted packet (not already sliced by current function activation)</t>
-  </si>
-  <si>
-    <t>1 - retain all</t>
-  </si>
-  <si>
-    <t>1 - no damage</t>
-  </si>
-  <si>
-    <t>1 - no charge</t>
-  </si>
-  <si>
-    <t>2 - retain only activating user specials</t>
-  </si>
-  <si>
-    <t>targeteting</t>
-  </si>
-  <si>
     <t>0 - random</t>
   </si>
   <si>
@@ -939,19 +1007,16 @@
     <t>special packet treatment</t>
   </si>
   <si>
-    <t>runs consist of 4 battles 1 intro 2&amp;3 escalation 4 boss, currently only difficulty progression is increased ice for each won battle</t>
-  </si>
-  <si>
     <t>2 - retain only for activating user</t>
   </si>
   <si>
-    <t>during a run SYSTEM ICE starts at the system base ICE then this increases by 50 after the player wins a battle - for the current 4 battle system its +0, +50, +100, +150</t>
-  </si>
-  <si>
-    <t>upgrades can't be duplicated, if there are less than 4 in the datasheet the game should error, each choice should be a unique upgrade but if there are fewer upgrades in the pool than the available number of route choices then the an upgrade can be listed in multiple choices</t>
-  </si>
-  <si>
-    <t>the game starts with an upgrade choice before the first battle but the system and host for both choices  always be DOORMAN and THRESHOLD</t>
+    <t>at the end of each boss turn add 3 special "override" specials to the board, placed randomly on any axis packet including overwriting player specials</t>
+  </si>
+  <si>
+    <t>if there are not enough valid targets for override packets activate function FNC_018 then repeat attempt to place until either all 3 overrides are placed or player is defeated</t>
+  </si>
+  <si>
+    <t>at the start of each boss turn if there are 15 override specials on board activate FNC_020 then if the player is still alive activate FNC_019 and continue the normal turn</t>
   </si>
 </sst>
 </file>
@@ -1022,6 +1087,14 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1273,115 +1346,115 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1393,18 +1466,94 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="B4" s="1"/>
     </row>
@@ -1414,10 +1563,10 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7">
@@ -1425,7 +1574,7 @@
         <v>0.0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
@@ -1433,7 +1582,7 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -1441,7 +1590,7 @@
         <v>2.0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10">
@@ -1449,7 +1598,7 @@
         <v>3.0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1457,7 +1606,7 @@
         <v>4.0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -1465,7 +1614,7 @@
         <v>5.0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13">
@@ -1473,7 +1622,7 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14">
@@ -1481,37 +1630,37 @@
         <v>7.0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>246</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>249</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20">
@@ -1519,10 +1668,10 @@
         <v>3</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21">
@@ -1530,43 +1679,43 @@
         <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>256</v>
+        <v>293</v>
       </c>
     </row>
     <row r="25">
@@ -1574,10 +1723,10 @@
         <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
     </row>
     <row r="26">
@@ -1585,109 +1734,109 @@
         <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>263</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>265</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>270</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>271</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>272</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>277</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>278</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>279</v>
+        <v>318</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>280</v>
+        <v>320</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>248</v>
+        <v>281</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>281</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -1698,7 +1847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1753,7 +1902,7 @@
         <v>258</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>262</v>
@@ -1783,16 +1932,16 @@
     <row r="3">
       <c r="A3" s="3"/>
       <c r="B3" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -1819,16 +1968,16 @@
     <row r="4">
       <c r="A4" s="3"/>
       <c r="B4" s="4" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
@@ -1855,10 +2004,12 @@
     <row r="5">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>285</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
@@ -1915,19 +2066,19 @@
         <v>115</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1953,19 +2104,19 @@
     <row r="8">
       <c r="A8" s="3"/>
       <c r="B8" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -1991,19 +2142,19 @@
     <row r="9">
       <c r="A9" s="3"/>
       <c r="B9" s="4" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -2031,7 +2182,7 @@
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="4" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -2086,16 +2237,16 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2123,13 +2274,13 @@
     <row r="13">
       <c r="A13" s="3"/>
       <c r="B13" s="4" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2157,13 +2308,13 @@
     <row r="14">
       <c r="A14" s="3"/>
       <c r="B14" s="4" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2221,10 +2372,10 @@
         <v>123</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2253,10 +2404,10 @@
     <row r="17">
       <c r="A17" s="3"/>
       <c r="B17" s="4" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2285,10 +2436,10 @@
     <row r="18">
       <c r="A18" s="3"/>
       <c r="B18" s="4" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2318,7 +2469,7 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -29848,7 +29999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -29858,7 +30009,7 @@
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="s">
-        <v>305</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -29866,23 +30017,55 @@
     </row>
     <row r="4">
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="1" t="s">
-        <v>308</v>
+        <v>263</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="1" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -29905,129 +30088,129 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>83</v>
@@ -30035,19 +30218,19 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -30064,6 +30247,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="8.13"/>
+    <col customWidth="1" min="2" max="2" width="15.75"/>
     <col customWidth="1" min="3" max="3" width="4.0"/>
     <col customWidth="1" min="4" max="4" width="19.25"/>
     <col customWidth="1" min="5" max="5" width="47.38"/>
@@ -30077,7 +30261,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -30089,51 +30273,51 @@
         <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1">
         <v>7.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="F2" s="1">
         <v>2.0</v>
@@ -30142,27 +30326,27 @@
         <v>2.0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1">
         <v>8.0</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F3" s="1">
         <v>1.0</v>
@@ -30173,19 +30357,19 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C4" s="1">
         <v>10.0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4" s="1">
         <v>30.0</v>
@@ -30193,7 +30377,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>92</v>
@@ -30210,7 +30394,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>95</v>
@@ -30219,7 +30403,7 @@
         <v>7.0</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="F6" s="1">
         <v>1.0</v>
@@ -30231,12 +30415,12 @@
         <v>96</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>97</v>
@@ -30282,7 +30466,7 @@
         <v>5.0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>105</v>
@@ -30294,10 +30478,10 @@
         <v>2.0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
@@ -30348,7 +30532,7 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>114</v>
@@ -30372,7 +30556,7 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>118</v>
@@ -30381,7 +30565,7 @@
         <v>5.0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>119</v>
@@ -30398,7 +30582,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>122</v>
@@ -30431,7 +30615,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>128</v>
@@ -30440,7 +30624,7 @@
         <v>9.0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>129</v>
@@ -30466,7 +30650,7 @@
         <v>7.0</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>131</v>
@@ -30507,7 +30691,7 @@
         <v>136</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>137</v>
@@ -30536,10 +30720,70 @@
         <v>136</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="1">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J21" s="1">
+        <v>70.0</v>
       </c>
     </row>
   </sheetData>
@@ -30566,60 +30810,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C2" s="1">
         <v>100.0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -30643,110 +30887,110 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1">
         <v>100.0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D3" s="1">
         <v>100.0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D4" s="1">
         <v>100.0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -30755,6 +30999,85 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="5" max="5" width="16.13"/>
+    <col customWidth="1" min="6" max="6" width="15.88"/>
+    <col customWidth="1" min="7" max="8" width="39.75"/>
+    <col customWidth="1" min="9" max="9" width="21.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="1">
+        <v>100.0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30770,206 +31093,206 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="D6" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>133</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>138</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -30977,7 +31300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30991,48 +31314,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="C2" s="1">
         <v>50.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>108</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -31040,7 +31363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31053,160 +31376,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
